--- a/www/download/COUNTRY.ROU.rpA2.xlsx
+++ b/www/download/COUNTRY.ROU.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Romênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.200944842620698</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.30565803346184</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.707018579958228</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.882526813020703</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1.50713623441745</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.14389846899757</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2.89620026258149</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3.30480173923261</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3.31928164503775</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3.25701079222564</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2.91002210893393</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2.80465564467292</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2.43463024937312</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>2.49929403971849</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3.04146434603597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.503</t>
+          <t>5.93765069732347</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.379</t>
+          <t>6.0256384882079</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.023</t>
+          <t>6.64433703418663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.813</t>
+          <t>5.53438436315465</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>4.21374330497879</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.771</t>
+          <t>3.77090587488388</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.657</t>
+          <t>3.71905454932889</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>4.76820804181671</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.569</t>
+          <t>6.21808069582962</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>5.16212605862982</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.267</t>
+          <t>4.43470940634261</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>4.49306382947346</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>9.365</t>
+          <t>4.22168123175262</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9.366</t>
+          <t>3.95318352689354</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9.212</t>
+          <t>4.49523085222873</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>2.82384456464946</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.894</t>
+          <t>3.01649326584128</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.399</t>
+          <t>3.47214254093425</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5.182</t>
+          <t>2.66663600812913</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.971</t>
+          <t>2.7198894126121</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.882</t>
+          <t>2.18362174769623</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.787</t>
+          <t>2.04091886324485</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.138</t>
+          <t>2.8705571440834</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.24587615675059</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6.407</t>
+          <t>3.17885877344565</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>2.70165399628295</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>2.7621438280033</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>2.48695952242241</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6.513</t>
+          <t>2.27901365336955</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6.583</t>
+          <t>2.69396539321804</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17008.077</t>
+          <t>1.14465401710078</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17598.162</t>
+          <t>1.18510606354117</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16800.278</t>
+          <t>1.53912126836488</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16391.695</t>
+          <t>0.949984061749807</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20083.159</t>
+          <t>1.18059436380255</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19959.764</t>
+          <t>0.830950789300175</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19742.438</t>
+          <t>0.64382455438641</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17876.156</t>
+          <t>1.04974842445707</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17579.559</t>
+          <t>0.728851056146229</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17371.251</t>
+          <t>1.25286490564866</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>17171.308</t>
+          <t>0.924438772289211</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17305.201</t>
+          <t>1.01984568372985</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17588.497</t>
+          <t>0.856553006043605</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17593.169</t>
+          <t>0.706667800060457</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17338.698</t>
+          <t>0.964412571460932</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11128.807</t>
+          <t>39035940403.6007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11394.243</t>
+          <t>40652922343.6869</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10468.573</t>
+          <t>35421677970.6287</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10026.345</t>
+          <t>32276875904.3848</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11606.427</t>
+          <t>38522560686.9584</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11478.276</t>
+          <t>37211965582.7385</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11318.912</t>
+          <t>37386309824.0792</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11929.299</t>
+          <t>34388393603.7337</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11555.4</t>
+          <t>34972907614.5233</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12477.476</t>
+          <t>34656113457.7927</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11991.971</t>
+          <t>34546151891.5791</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12430.286</t>
+          <t>35191230397.185</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>12497.741</t>
+          <t>36207387251.6029</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>12629.99</t>
+          <t>37229118602.2318</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12762.814</t>
+          <t>35917650235.3756</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>5914935649.40073</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>5915224247.64478</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>4727920542.39135</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>5722542488.01839</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>6337967365.2759</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>7373001063.97284</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>7907846711.97413</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>6720220317.46321</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>6823255081.74369</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>6627638014.73443</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>7427869014.14718</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>7469463647.13866</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>8108708001.4855</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>8897465216.66149</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>7988666235.98208</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>16300306.2759229</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>15345864.8727196</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>14646164.1773322</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>12757902.8779274</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>14860351.601295</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>14154183.4847741</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12687760.3713827</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>11309144.8371299</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>9267818.65761898</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>7060756.10390742</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>5750418.63729243</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>4974044.90096201</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>3757391.1415427</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>3211997.13396554</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>3924831.82094994</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>88572.6621036034</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>89237.6655099733</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>81151.8192416026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>76166.5663247051</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>92227.8116933028</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>91578.9200334266</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>87956.9220614255</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>82488.118337865</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>89209.4594311383</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>94988.3165790773</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>100871.242442139</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>106466.289213186</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>120538.750440644</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>134774.866208726</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>124777.524864478</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>170280.601212041</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>176792.574447604</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>151503.35695343</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>136351.025063991</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>167900.580678609</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>163113.494745734</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>158085.626843946</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>147278.461677211</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>160365.266306306</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>172357.086857313</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>182748.36048887</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>193753.611291603</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>223476.691898532</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>251014.904935761</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>223840.618993325</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>2.17044306966418</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.23093651568705</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>2.63579867575155</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>1.83781253279324</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>1.96384680707255</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>1.55240055786079</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>1.36391249964746</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>1.98592194645438</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>2.00237311902364</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>2.4202295637925</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>2.01420771684379</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>2.13825317410207</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>1.91686727161334</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>1.75920527556001</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>2.18876040611926</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>8621.88665148551</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>9226.6580996365</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>9071.52692359665</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>10080.3634535941</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>8992.88718455405</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>9722.7172574683</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>10712.9624327706</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>12003.1931111439</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>15137.8121786785</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>18726.5610163955</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>23707.9999548669</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>29239.72564936</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>39551.4044013844</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>46167.2743920515</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>39101.4384900643</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.200944842620698</t>
+          <t>1017.34210669053</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.30565803346184</t>
+          <t>1003.59917039581</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.707018579958228</t>
+          <t>875.673358508297</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.882526813020703</t>
+          <t>1104.37568992524</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.50713623441745</t>
+          <t>1061.4582758794</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.14389846899757</t>
+          <t>1253.59195170838</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.89620026258149</t>
+          <t>1366.55550002145</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.30480173923261</t>
+          <t>1094.90856794291</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.31928164503775</t>
+          <t>1156.42511088312</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.25701079222564</t>
+          <t>1034.35630350908</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.91002210893393</t>
+          <t>1205.39239462322</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.80465564467292</t>
+          <t>1164.9921465997</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.43463024937312</t>
+          <t>1259.80082365968</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.49929403971849</t>
+          <t>1366.10858539252</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.04146434603597</t>
+          <t>1213.51363032299</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-2082318700.03371</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-2278957744.75968</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-2430984630.29859</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-1880506761.98548</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-3024749171.14563</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-2614683288.52166</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-2353906668.3175</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2580045068.64068</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2215277014.38574</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-1673150092.03307</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>-1369029410.89625</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-1062305204.38239</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-1381425485.38395</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>-1482722506.66138</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-784951454.918619</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2087744440.15087</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2266092722.28327</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2476407530.8127</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-1974194456.00322</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-3189506319.07308</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2810823383.72243</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-2590426318.93104</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-2907414743.96924</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-2696323283.84898</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-2146993769.56556</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>-1938572706.77537</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1859446510.09587</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-2149747943.57137</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2503980496.18926</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-1903739194.38288</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>5425740.1171645</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>-12865022.4764017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>45422900.5141093</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>93687694.0177416</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>164757147.927453</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>196140095.200775</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>236519650.613542</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>327369675.328555</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>481046269.463232</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>473843677.532496</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>569543295.879124</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>797141305.713479</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>768322458.187426</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>1021257989.52788</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>1118787739.46426</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>3225.42523163455</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>3242.56520674505</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>3183.77203725538</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>3134.01117378204</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>3145.9997218059</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3199.66879687027</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>3230.41762796269</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>3269.31152238168</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>3472.01966707942</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>3537.73600875689</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>3633.30305769812</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>3656.0403018705</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>3674.67179128444</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>3769.37401580286</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>3869.60421666001</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>2682.24406527007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>2797.87227783984</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>2696.8641198065</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>2659.34581055875</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2566.18322593583</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>2588.28005509426</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2602.75349803549</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>2769.34612421364</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>2828.10065676768</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>2987.95752425558</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>3041.56490584039</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>3096.09434302852</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>3158.17201502971</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>3239.35017107222</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>3352.17395811184</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>593.77</t>
+          <t>9015.42516999499</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>602.56</t>
+          <t>9424.89168999499</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>664.43</t>
+          <t>9716.80211999499</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>553.44</t>
+          <t>9329.596589995</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>421.37</t>
+          <t>9671.49620999501</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>377.09</t>
+          <t>11602.476589995</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>371.91</t>
+          <t>12503.776749996</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>476.82</t>
+          <t>14965.508649996</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>621.81</t>
+          <t>18960.547039996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>516.21</t>
+          <t>25567.907739996</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>443.47</t>
+          <t>31153.799929996</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>449.31</t>
+          <t>38170.103819996</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>422.17</t>
+          <t>48894.796309996</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>395.32</t>
+          <t>60280.244599996</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>449.52</t>
+          <t>46893.386289996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>282.38</t>
+          <t>4326901311.5856</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>301.65</t>
+          <t>4442390893.58522</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>347.21</t>
+          <t>4276558679.59883</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>266.66</t>
+          <t>3681721887.99941</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>271.99</t>
+          <t>5106382578.55966</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>218.36</t>
+          <t>5318224028.1364</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>204.09</t>
+          <t>5278444398.30523</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>287.06</t>
+          <t>5780817688.45905</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>424.59</t>
+          <t>5888467211.29614</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>317.89</t>
+          <t>6050783573.6099</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>270.17</t>
+          <t>5793682672.64597</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>276.21</t>
+          <t>5898430734.27711</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>248.7</t>
+          <t>5554607008.62022</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>227.9</t>
+          <t>6065386959.88552</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>5672791230.97606</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>114.47</t>
+          <t>10941.0688131599</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>118.51</t>
+          <t>12150.2883833094</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>153.91</t>
+          <t>11887.9487200439</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>12425.0202418549</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>118.06</t>
+          <t>11308.9760301437</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>13620.5575021578</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>64.38</t>
+          <t>15604.343044409</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>104.97</t>
+          <t>17610.5644620268</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>23491.8781941283</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>125.29</t>
+          <t>32323.2803527197</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>92.44</t>
+          <t>41395.4874568987</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>101.98</t>
+          <t>52856.4065527493</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>71798.6577295149</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>86273.899594741</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>96.44</t>
+          <t>56842.500007713</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25489.58</t>
+          <t>2798354278.62276</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26240.918</t>
+          <t>2930521557.86418</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24332.705</t>
+          <t>2413948747.80094</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23435.489</t>
+          <t>2663612387.36194</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>27856.945</t>
+          <t>2555405594.95032</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>27879.4</t>
+          <t>3300136178.9205</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27738.585</t>
+          <t>3895607834.55813</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26513.72</t>
+          <t>4027725863.75112</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27063.509</t>
+          <t>5014883530.42577</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28117.278</t>
+          <t>6232164864.73075</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>28187.094</t>
+          <t>7043269106.08928</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>28889.656</t>
+          <t>8287135850.73551</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29575.965</t>
+          <t>8951314443.20478</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>30340.726</t>
+          <t>9487236423.47522</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>30880.209</t>
+          <t>6981250691.03999</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18752.967</t>
+          <t>-1925.6436431649</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19111.714</t>
+          <t>-2725.39669331438</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17189.767</t>
+          <t>-2171.14660004895</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16239.503</t>
+          <t>-3095.4236518599</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18784.764</t>
+          <t>-1637.47982014866</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18818.852</t>
+          <t>-2018.08091216285</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18693.458</t>
+          <t>-3100.56629441306</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20066.053</t>
+          <t>-2645.05581203082</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20485.958</t>
+          <t>-4531.33115413229</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22668.043</t>
+          <t>-6755.37261272371</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22389.14</t>
+          <t>-10241.6875269028</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>23441.068</t>
+          <t>-14686.3027327534</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23652.025</t>
+          <t>-22903.8614195189</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24549.933</t>
+          <t>-25993.654994745</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>25473.943</t>
+          <t>-9949.11371771708</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>39035.94</t>
+          <t>1528547032.96285</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>40652.922</t>
+          <t>1511869335.72104</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35421.678</t>
+          <t>1862609931.79789</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>32276.876</t>
+          <t>1018109500.63747</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>38522.561</t>
+          <t>2550976983.60934</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>37211.966</t>
+          <t>2018087849.2159</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>37386.31</t>
+          <t>1382836563.7471</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>34388.394</t>
+          <t>1753091824.70793</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>34972.908</t>
+          <t>873583680.87037</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>34656.113</t>
+          <t>-181381291.120844</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>34546.152</t>
+          <t>-1249586433.44331</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>35191.23</t>
+          <t>-2388705116.45841</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>36207.387</t>
+          <t>-3396707434.58456</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>37229.119</t>
+          <t>-3421849463.58971</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>35917.65</t>
+          <t>-1308459460.06393</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>23336.75252</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>23380.70425</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>21982.16619</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>22614.83698</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>19009.69485</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>19167.23233</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>22411.43356</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>25121.62818</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>31505.19079</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>41573.58063</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>51146.00313</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>62791.13112</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>86627.44546</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>107462.62559</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>86061.9317</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20304.821</t>
+          <t>0.0468852601715154</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20519.934</t>
+          <t>0.0372023652659323</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18973.399</t>
+          <t>0.0511045317952406</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>18030.072</t>
+          <t>0.0137261834673306</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21160.448</t>
+          <t>0.0349131014342507</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20892.395</t>
+          <t>0.0137975000558591</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20801.289</t>
+          <t>-0.00702466947949518</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19260.344</t>
+          <t>0.00130292596700262</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19455.049</t>
+          <t>-0.00116979739316858</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19099.452</t>
+          <t>0.0486517803691368</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19068.369</t>
+          <t>0.0244885589378601</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>19337.341</t>
+          <t>0.0264538149655801</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>19529.523</t>
+          <t>0.0369828588069823</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>19989.05</t>
+          <t>0.0306400721069742</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>20021.904</t>
+          <t>0.033486575909399</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>14284.517009183</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>14117.410760155</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>11690.0745960578</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>16021.0430218163</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>12696.4634033637</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>14925.8000167552</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>16857.3288552141</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>18209.382789563</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>22301.843613053</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>28061.4360667414</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>38830.2546278648</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>47134.0930612798</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>66514.4530613812</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>86485.0219131855</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>66985.0361892292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5914.936</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5915.224</t>
+          <t>20827.7154125453</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4727.921</t>
+          <t>17878.2323324753</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5722.542</t>
+          <t>25574.5068786929</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6337.967</t>
+          <t>19246.946945127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7373.001</t>
+          <t>22387.8492687505</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7907.847</t>
+          <t>26932.9122035333</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6720.22</t>
+          <t>29223.1540073207</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6823.255</t>
+          <t>38004.1607531317</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>6627.638</t>
+          <t>37815.7515167356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>7427.869</t>
+          <t>56716.3153914071</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7469.464</t>
+          <t>70036.737127413</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>8108.708</t>
+          <t>94380.2326877114</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>8897.465</t>
+          <t>120176.419878924</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>7988.666</t>
+          <t>91760.5600450726</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>217.04</t>
+          <t>134405.670555828</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>223.09</t>
+          <t>138291.398437762</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>263.58</t>
+          <t>128341.58407335</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>183.78</t>
+          <t>140767.682605421</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>196.38</t>
+          <t>125102.10611178</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>131661.510884344</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>136.39</t>
+          <t>143033.378187658</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>198.59</t>
+          <t>157317.857442779</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>200.24</t>
+          <t>193740.910292466</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>242.02</t>
+          <t>232061.861481868</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>201.42</t>
+          <t>297438.897168626</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>213.83</t>
+          <t>348189.400856234</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>191.69</t>
+          <t>469596.611271851</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>175.92</t>
+          <t>558820.926701643</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>218.88</t>
+          <t>489307.462464804</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.346</t>
+          <t>21595.0366867756</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.646</t>
+          <t>18568.8891500682</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>12.758</t>
+          <t>22952.3748023089</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>20618.1891217812</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.154</t>
+          <t>23217.9821996451</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.688</t>
+          <t>27580.3621459438</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.309</t>
+          <t>27991.1338055133</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.268</t>
+          <t>29848.6267121628</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.061</t>
+          <t>24378.2663766318</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>31500.6716348722</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>34498.1691028764</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.757</t>
+          <t>35897.1168923718</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.212</t>
+          <t>39692.5976931957</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>34014.9487228104</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>14284.517009183</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14761.3062974795</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12169.3016784859</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>13975.4343761728</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12548.8282212418</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>14549.9339435519</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16120.6752889863</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>15916.0977565602</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16058.847195775</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>17122.527383603</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>19040.4391163132</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>20032.3729149732</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>21698.0059961549</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>24743.7870455706</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>21639.7454171529</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14923.5314840225</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>14371.4252174547</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15630.3634875247</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>12012.5664913071</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>13360.589704873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>11539.3169612495</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9708.20022646666</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>12208.1666326793</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>14911.1745668683</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>30016.7837332644</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>30991.8499185929</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>38450.663632587</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>56918.4295722886</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>63289.5878810759</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>55486.6699749274</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>18752966737.1521</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19111714020.193</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>17189767247.085</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>16239502791.9404</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>18784764338.903</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>18818852028.7925</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>18693457687.7317</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20066053330.922</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>20485957641.6687</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>22668043476.1097</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>22389140102.1473</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>23441067999.4729</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>23652024984.6023</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>24549932964.924</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>25473942591.0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>25489580305.8645</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>26240917715.1982</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>24332705391.4853</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>23435489378.3416</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>27856945390.8238</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>27879399785.4423</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>27738585129.9635</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>26513719793.2214</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>27063509234.9383</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>28117277894.7499</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>28187094451.8946</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>28889656314.7991</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>29575965103.5518</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>30340725507.3137</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>30880208553.2599</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20304821187.2301</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20519933585.6949</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18973398779.476</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>18030072074.4258</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>21160447799.65</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>20892395357.6034</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20801288548.5596</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19260344307.8519</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>19455049431.1378</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>19099451821.5226</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>19068369497.6879</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>19337341318.4837</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19529523096.7995</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>19989049972.824</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>20021904493.8034</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9503080.13946449</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9378883.34754797</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9022592.28144989</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8812501.66311301</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10855400</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10771400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10657400</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9574000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9569500</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9410200</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9267300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>9331000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>9364900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>9366300</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>9211994.64560414</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5814106.78915309</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5894010.69882498</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>5399182.80766852</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5181699.07235622</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5971000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5881500</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5786700</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6137700</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5900300</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6407500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6162200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>6411600</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6436500</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6513000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6583087.35589215</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>17008076566.2517</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>17598162191.4035</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16800278404.2581</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>16391695466.7451</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20083159000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>19959764000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19742438000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>17876156000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17579559000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17371251000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17171308000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17305201000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>17588497000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>17593169000</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>17338697861.6088</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>11128807489.9963</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11394243144.4763</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10468573057.614</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10026345038.1371</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>11606427000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11478276000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11318912000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11929299000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>11555400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>12477476000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>11991971000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>12430286000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>12497741000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>12629990000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>12762813634.0076</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.233175632421713</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.23253959469975</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.220194395322882</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.20815449878133</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.211434792120948</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.215353752477266</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.21580284304186</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.223774869612283</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.261459806563282</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.266378193511664</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.279458030492262</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.286412987163339</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.298013364501723</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.318452698794842</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.329335976037564</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.223112108065907</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.23076560909183</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.222322563509499</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.213259917236434</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.230516427377225</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.236222063272243</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.243682664860547</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.24066817692975</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.235794531713251</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.246454552404253</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.246466736759821</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.255423644330556</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.247899377409721</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.244786230180686</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.261406427925119</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.54371225951238</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.536694796208419</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.557483041167619</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.578585583982235</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.558048780501827</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.548424184250491</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.540514492097593</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.535556953457967</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.502745661723467</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.487167254084083</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.474075232747917</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.458163368506105</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.454087258088556</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.436761071024472</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.409257596037317</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>79644.24419</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>82950.2155</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>76895.00852</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>80843.09454</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>72237.66396</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>73192.59749</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>78998.85387</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>89452.53788</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>115044.05127</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>148577.15376</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>188278.39696</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>234079.32454</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>322023.23116</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>394379.72946</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>312861.4044</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>35877.50728</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>35199.14063</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>33508.59582</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>37587.07337</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>32607.53665</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>33927.16623</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>36641.11243</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>41431.32064</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>52915.33532</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>67832.53525</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>87708.16531</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>108487.40076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>151298.66226</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>183466.00776</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>147247.23002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>27008.1262578989</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>27560.7777695561</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>28102.593183816</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>28512.4330760852</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>28817.1042268573</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29192.1470307955</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>29694.9838785975</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30317.3124995246</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31062.735151797</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>31986.3200668522</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33198.7943111179</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34855.640122582</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>37358.6348316571</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>40334.0438289789</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>41909.9936147802</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
